--- a/meter_data.xlsx
+++ b/meter_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,536 +519,30 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>38384</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>37485</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>38475</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38473</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>38583</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>38485</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C3" t="n">
-        <v>72</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>06.2025</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>111</v>
-      </c>
-      <c r="H3" t="n">
-        <v>222</v>
-      </c>
-      <c r="I3" t="n">
-        <v>333</v>
-      </c>
-      <c r="J3" t="n">
-        <v>444</v>
-      </c>
-      <c r="K3" t="n">
-        <v>56665</v>
-      </c>
-      <c r="L3" t="n">
-        <v>666</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C4" t="n">
-        <v>72</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C5" t="n">
-        <v>72</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C7" t="n">
-        <v>72</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C8" t="n">
-        <v>72</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C9" t="n">
-        <v>72</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C10" t="n">
-        <v>72</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>&lt;attribute 'month' of 'datetime.date' objects&gt;.&lt;attribute 'year' of 'datetime.date' objects&gt;</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C11" t="n">
-        <v>72</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.2025</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C12" t="n">
-        <v>72</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>06.2025</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>5433018703</v>
-      </c>
-      <c r="C13" t="n">
-        <v>72</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>06.2025</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
